--- a/artfynd/A 43271-2024 artfynd.xlsx
+++ b/artfynd/A 43271-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150597</v>
       </c>
       <c r="B2" t="n">
-        <v>89743</v>
+        <v>89753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150598</v>
+        <v>121150599</v>
       </c>
       <c r="B3" t="n">
-        <v>90973</v>
+        <v>97041</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>794176</v>
+        <v>794430</v>
       </c>
       <c r="R3" t="n">
-        <v>7385602</v>
+        <v>7385512</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150599</v>
+        <v>121150598</v>
       </c>
       <c r="B4" t="n">
-        <v>97031</v>
+        <v>90983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>794430</v>
+        <v>794176</v>
       </c>
       <c r="R4" t="n">
-        <v>7385512</v>
+        <v>7385602</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 43271-2024 artfynd.xlsx
+++ b/artfynd/A 43271-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150597</v>
+        <v>121150598</v>
       </c>
       <c r="B2" t="n">
-        <v>89753</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>794341</v>
+        <v>794176</v>
       </c>
       <c r="R2" t="n">
-        <v>7385422</v>
+        <v>7385602</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150599</v>
+        <v>121150597</v>
       </c>
       <c r="B3" t="n">
-        <v>97041</v>
+        <v>89753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>794430</v>
+        <v>794341</v>
       </c>
       <c r="R3" t="n">
-        <v>7385512</v>
+        <v>7385422</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150598</v>
+        <v>121150599</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>97041</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>794176</v>
+        <v>794430</v>
       </c>
       <c r="R4" t="n">
-        <v>7385602</v>
+        <v>7385512</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 43271-2024 artfynd.xlsx
+++ b/artfynd/A 43271-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150598</v>
+        <v>121150599</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>97054</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>794176</v>
+        <v>794430</v>
       </c>
       <c r="R2" t="n">
-        <v>7385602</v>
+        <v>7385512</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>121150597</v>
       </c>
       <c r="B3" t="n">
-        <v>89753</v>
+        <v>89760</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150599</v>
+        <v>121150598</v>
       </c>
       <c r="B4" t="n">
-        <v>97041</v>
+        <v>90995</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>794430</v>
+        <v>794176</v>
       </c>
       <c r="R4" t="n">
-        <v>7385512</v>
+        <v>7385602</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 43271-2024 artfynd.xlsx
+++ b/artfynd/A 43271-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150599</v>
+        <v>121150597</v>
       </c>
       <c r="B2" t="n">
-        <v>97054</v>
+        <v>89761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>794430</v>
+        <v>794341</v>
       </c>
       <c r="R2" t="n">
-        <v>7385512</v>
+        <v>7385422</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150597</v>
+        <v>121150598</v>
       </c>
       <c r="B3" t="n">
-        <v>89760</v>
+        <v>90996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>794341</v>
+        <v>794176</v>
       </c>
       <c r="R3" t="n">
-        <v>7385422</v>
+        <v>7385602</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150598</v>
+        <v>121150599</v>
       </c>
       <c r="B4" t="n">
-        <v>90995</v>
+        <v>97055</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>794176</v>
+        <v>794430</v>
       </c>
       <c r="R4" t="n">
-        <v>7385602</v>
+        <v>7385512</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 43271-2024 artfynd.xlsx
+++ b/artfynd/A 43271-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150597</v>
+        <v>121150599</v>
       </c>
       <c r="B2" t="n">
-        <v>89761</v>
+        <v>97058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>794341</v>
+        <v>794430</v>
       </c>
       <c r="R2" t="n">
-        <v>7385422</v>
+        <v>7385512</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150598</v>
+        <v>121150597</v>
       </c>
       <c r="B3" t="n">
-        <v>90996</v>
+        <v>89764</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>794176</v>
+        <v>794341</v>
       </c>
       <c r="R3" t="n">
-        <v>7385602</v>
+        <v>7385422</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150599</v>
+        <v>121150598</v>
       </c>
       <c r="B4" t="n">
-        <v>97055</v>
+        <v>90999</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>794430</v>
+        <v>794176</v>
       </c>
       <c r="R4" t="n">
-        <v>7385512</v>
+        <v>7385602</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 43271-2024 artfynd.xlsx
+++ b/artfynd/A 43271-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150597</v>
+        <v>121150598</v>
       </c>
       <c r="B3" t="n">
-        <v>89764</v>
+        <v>90999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>794341</v>
+        <v>794176</v>
       </c>
       <c r="R3" t="n">
-        <v>7385422</v>
+        <v>7385602</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150598</v>
+        <v>121150597</v>
       </c>
       <c r="B4" t="n">
-        <v>90999</v>
+        <v>89764</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>794176</v>
+        <v>794341</v>
       </c>
       <c r="R4" t="n">
-        <v>7385602</v>
+        <v>7385422</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
